--- a/DATA/DATA FILES/STOCKED CHILLERS DATA.xlsx
+++ b/DATA/DATA FILES/STOCKED CHILLERS DATA.xlsx
@@ -721,6 +721,11 @@
           <t>R-454B</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>QTC3040THJ17VSD</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -823,6 +828,11 @@
           <t>R-454B</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>QTC3040THJ46VSD</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -925,6 +935,11 @@
           <t>R-454B</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>QTC3050THJ17VSD</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1027,6 +1042,11 @@
           <t>R-454B</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>QTC3050THJ46VSD</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1129,6 +1149,11 @@
           <t>R-454B</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>QTC3055THJ17VSD</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1231,6 +1256,11 @@
           <t>R-454B</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>QTC3055THJ46VSD</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1333,6 +1363,11 @@
           <t>R-454B</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>QTC3060THJ17VSD</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1435,6 +1470,11 @@
           <t>R-454B</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>QTC3060THJ46VSD</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1537,6 +1577,11 @@
           <t>R-454B</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>QTC3070TSJ46VSD</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1639,6 +1684,11 @@
           <t>R-454B</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>QTC3075TSJ46VSD</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1741,6 +1791,11 @@
           <t>R-454B</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>QTC3085TSJ17VSD</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1843,6 +1898,11 @@
           <t>R-454B</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>QTC3085TSJ46VSD</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1945,6 +2005,11 @@
           <t>R-454B</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>QTC3095TSJ17PC</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2047,6 +2112,11 @@
           <t>R-454B</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>QTC3095TSJ46VSD</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2149,6 +2219,11 @@
           <t>R-454B</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>QTC3110TSJ17VSD</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2251,6 +2326,11 @@
           <t>R-454B</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>QTC3110TSJ46VSD</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2353,6 +2433,11 @@
           <t>R-454B</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>QTC3129THJ17VSD</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2455,6 +2540,11 @@
           <t>R-454B</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>QTC3129THJ46VSD</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2557,6 +2647,11 @@
           <t>R-454B</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>QTC3140TSJ17VSD</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2659,6 +2754,11 @@
           <t>R-454B</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>QTC3140TSJ46VSD</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2761,6 +2861,11 @@
           <t>R-513A</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>QTC4150SXXX46R</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2863,6 +2968,11 @@
           <t>R-454B</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>QTC3160TSJ17VSD</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2965,6 +3075,11 @@
           <t>R-454B</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>QTC3160TSJ46VSD</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3067,6 +3182,11 @@
           <t>R-513A</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>QTC4185SXXX46R</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3169,6 +3289,11 @@
           <t>R-454B</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>QTC3205THJ46VSD</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3271,6 +3396,11 @@
           <t>R-513A</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>QTC4210SXXX46R</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3373,6 +3503,11 @@
           <t>R-454B</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>QTC3225THJ46VSD</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3475,6 +3610,11 @@
           <t>R-513A</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>QTC4230SXXX46R</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3577,6 +3717,11 @@
           <t>R-513A</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>QTC4270SXXX46R</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3677,6 +3822,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>R-513A</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>QTC4340SXXX46R</t>
         </is>
       </c>
     </row>
@@ -3794,9 +3944,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-    </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>

--- a/DATA/DATA FILES/STOCKED CHILLERS DATA.xlsx
+++ b/DATA/DATA FILES/STOCKED CHILLERS DATA.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD34"/>
+  <dimension ref="A1:AE34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -435,6 +435,8 @@
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="22" customWidth="1" min="22" max="22"/>
     <col width="16" customWidth="1" min="26" max="26"/>
+    <col width="13" customWidth="1" min="30" max="30"/>
+    <col width="13" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -490,6 +492,11 @@
           <t>ENGINEERING MANUAL</t>
         </is>
       </c>
+      <c r="AE2" s="1" t="inlineStr">
+        <is>
+          <t>INSTALLATION MANUAL</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -726,6 +733,16 @@
           <t>QTC3040THJ17VSD</t>
         </is>
       </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Quantech QTC3 Engineering Guide QTC3-EG6</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>Quantech QTC3 IOM QTC3-NM1</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -833,6 +850,16 @@
           <t>QTC3040THJ46VSD</t>
         </is>
       </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Quantech QTC3 Engineering Guide QTC3-EG6</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>Quantech QTC3 IOM QTC3-NM1</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -940,6 +967,16 @@
           <t>QTC3050THJ17VSD</t>
         </is>
       </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Quantech QTC3 Engineering Guide QTC3-EG6</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>Quantech QTC3 IOM QTC3-NM1</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1047,6 +1084,16 @@
           <t>QTC3050THJ46VSD</t>
         </is>
       </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>Quantech QTC3 Engineering Guide QTC3-EG6</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>Quantech QTC3 IOM QTC3-NM1</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1154,6 +1201,16 @@
           <t>QTC3055THJ17VSD</t>
         </is>
       </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>Quantech QTC3 Engineering Guide QTC3-EG6</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>Quantech QTC3 IOM QTC3-NM1</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1261,6 +1318,16 @@
           <t>QTC3055THJ46VSD</t>
         </is>
       </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>Quantech QTC3 Engineering Guide QTC3-EG6</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>Quantech QTC3 IOM QTC3-NM1</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1368,6 +1435,16 @@
           <t>QTC3060THJ17VSD</t>
         </is>
       </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>Quantech QTC3 Engineering Guide QTC3-EG6</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>Quantech QTC3 IOM QTC3-NM1</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1475,6 +1552,16 @@
           <t>QTC3060THJ46VSD</t>
         </is>
       </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>Quantech QTC3 Engineering Guide QTC3-EG6</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>Quantech QTC3 IOM QTC3-NM1</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1582,6 +1669,16 @@
           <t>QTC3070TSJ46VSD</t>
         </is>
       </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>Quantech QTC3 Engineering Guide QTC3-EG6</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>Quantech QTC3 IOM QTC3-NM1</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1689,6 +1786,16 @@
           <t>QTC3075TSJ46VSD</t>
         </is>
       </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>Quantech QTC3 Engineering Guide QTC3-EG6</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>Quantech QTC3 IOM QTC3-NM1</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1796,6 +1903,16 @@
           <t>QTC3085TSJ17VSD</t>
         </is>
       </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>Quantech QTC3 Engineering Guide QTC3-EG6</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>Quantech QTC3 IOM QTC3-NM1</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1903,6 +2020,16 @@
           <t>QTC3085TSJ46VSD</t>
         </is>
       </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>Quantech QTC3 Engineering Guide QTC3-EG6</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>Quantech QTC3 IOM QTC3-NM1</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2010,6 +2137,16 @@
           <t>QTC3095TSJ17PC</t>
         </is>
       </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>Quantech QTC3 Engineering Guide QTC3-EG6</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>Quantech QTC3 IOM QTC3-NM1</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2117,6 +2254,16 @@
           <t>QTC3095TSJ46VSD</t>
         </is>
       </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>Quantech QTC3 Engineering Guide QTC3-EG6</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>Quantech QTC3 IOM QTC3-NM1</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2224,6 +2371,16 @@
           <t>QTC3110TSJ17VSD</t>
         </is>
       </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>Quantech QTC3 Engineering Guide QTC3-EG6</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>Quantech QTC3 IOM QTC3-NM1</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2331,6 +2488,16 @@
           <t>QTC3110TSJ46VSD</t>
         </is>
       </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>Quantech QTC3 Engineering Guide QTC3-EG6</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>Quantech QTC3 IOM QTC3-NM1</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2438,6 +2605,16 @@
           <t>QTC3129THJ17VSD</t>
         </is>
       </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>Quantech QTC3 Engineering Guide QTC3-EG6</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>Quantech QTC3 IOM QTC3-NM1</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2545,6 +2722,16 @@
           <t>QTC3129THJ46VSD</t>
         </is>
       </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>Quantech QTC3 Engineering Guide QTC3-EG6</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>Quantech QTC3 IOM QTC3-NM1</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2652,6 +2839,16 @@
           <t>QTC3140TSJ17VSD</t>
         </is>
       </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>Quantech QTC3 Engineering Guide QTC3-EG6</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>Quantech QTC3 IOM QTC3-NM1</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2759,6 +2956,16 @@
           <t>QTC3140TSJ46VSD</t>
         </is>
       </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>Quantech QTC3 Engineering Guide QTC3-EG6</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>Quantech QTC3 IOM QTC3-NM1</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2866,6 +3073,16 @@
           <t>QTC4150SXXX46R</t>
         </is>
       </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>Quantech QTC4 Engineering Guide QTC4-EG2</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>Quantech QTC4 IOM QTC4-NM2</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2973,6 +3190,16 @@
           <t>QTC3160TSJ17VSD</t>
         </is>
       </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>Quantech QTC3 Engineering Guide QTC3-EG6</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>Quantech QTC3 IOM QTC3-NM1</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3080,6 +3307,16 @@
           <t>QTC3160TSJ46VSD</t>
         </is>
       </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>Quantech QTC3 Engineering Guide QTC3-EG6</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>Quantech QTC3 IOM QTC3-NM1</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3187,6 +3424,16 @@
           <t>QTC4185SXXX46R</t>
         </is>
       </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>Quantech QTC4 Engineering Guide QTC4-EG2</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>Quantech QTC4 IOM QTC4-NM2</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3294,6 +3541,16 @@
           <t>QTC3205THJ46VSD</t>
         </is>
       </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>Quantech QTC3 Engineering Guide QTC3-EG6</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>Quantech QTC3 IOM QTC3-NM1</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3401,6 +3658,16 @@
           <t>QTC4210SXXX46R</t>
         </is>
       </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>Quantech QTC4 Engineering Guide QTC4-EG2</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>Quantech QTC4 IOM QTC4-NM2</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3508,6 +3775,16 @@
           <t>QTC3225THJ46VSD</t>
         </is>
       </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>Quantech QTC3 Engineering Guide QTC3-EG6</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>Quantech QTC3 IOM QTC3-NM1</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3615,6 +3892,16 @@
           <t>QTC4230SXXX46R</t>
         </is>
       </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>Quantech QTC4 Engineering Guide QTC4-EG2</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>Quantech QTC4 IOM QTC4-NM2</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3722,6 +4009,16 @@
           <t>QTC4270SXXX46R</t>
         </is>
       </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>Quantech QTC4 Engineering Guide QTC4-EG2</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>Quantech QTC4 IOM QTC4-NM2</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3829,13 +4126,24 @@
           <t>QTC4340SXXX46R</t>
         </is>
       </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>Quantech QTC4 Engineering Guide QTC4-EG2</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>Quantech QTC4 IOM QTC4-NM2</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="23">
     <mergeCell ref="A2:V2"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="X1:AA1"/>
+    <mergeCell ref="AC1:AE1"/>
     <mergeCell ref="L3:P3"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="AA2:AA4"/>
@@ -3845,13 +4153,13 @@
     <mergeCell ref="X2:X4"/>
     <mergeCell ref="G3:K3"/>
     <mergeCell ref="A1:V1"/>
-    <mergeCell ref="AC1:AD1"/>
     <mergeCell ref="T3:T4"/>
     <mergeCell ref="Q3:S3"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="V3:V4"/>
     <mergeCell ref="Y2:Y4"/>
+    <mergeCell ref="AE2:AE4"/>
     <mergeCell ref="Z2:Z4"/>
     <mergeCell ref="AD2:AD4"/>
   </mergeCells>
@@ -3944,7 +4252,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
